--- a/doc/T-Jercleuett-BitRuisseau-321.xlsx
+++ b/doc/T-Jercleuett-BitRuisseau-321.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pt04ihk\Documents\GitHub\321-BitRuisseau\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F16D617-F575-4A54-BF25-E8B5B7839FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE6F43E-AF0D-4DF1-BA24-77A216CD1CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33870" yWindow="2355" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="18" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
   <si>
     <t>Apprenti.e</t>
   </si>
@@ -167,6 +167,21 @@
   </si>
   <si>
     <t>Créer le projet BitRuisseau</t>
+  </si>
+  <si>
+    <t>Scrum meeting seul</t>
+  </si>
+  <si>
+    <t>Modification pour choisir le dossier de fichiers audio</t>
+  </si>
+  <si>
+    <t>Modification pour afficher les fichiers du dossier</t>
+  </si>
+  <si>
+    <t>Gestion de projet</t>
+  </si>
+  <si>
+    <t>JDT</t>
   </si>
 </sst>
 </file>
@@ -470,51 +485,51 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -847,10 +862,10 @@
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="32"/>
+      <c r="C1" s="23"/>
       <c r="D1" s="22" t="s">
         <v>1</v>
       </c>
@@ -862,10 +877,10 @@
       <c r="A2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="32"/>
+      <c r="C2" s="23"/>
       <c r="D2" s="22" t="s">
         <v>4</v>
       </c>
@@ -877,10 +892,10 @@
       <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="32"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="22" t="s">
         <v>7</v>
       </c>
@@ -892,12 +907,12 @@
       <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -920,7 +935,7 @@
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="33">
         <v>45964</v>
       </c>
       <c r="C6" s="5">
@@ -935,7 +950,7 @@
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="24"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="8">
         <v>50</v>
       </c>
@@ -948,7 +963,7 @@
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="24"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="8">
         <v>60</v>
       </c>
@@ -961,14 +976,14 @@
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
-      <c r="B9" s="24"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
       <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
-      <c r="B10" s="25"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
       <c r="E10" s="10"/>
@@ -977,16 +992,16 @@
       <c r="A11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="28"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="32"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="33">
         <v>45971</v>
       </c>
       <c r="C12" s="5">
@@ -1003,7 +1018,7 @@
       <c r="A13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="24"/>
+      <c r="B13" s="28"/>
       <c r="C13" s="8">
         <v>20</v>
       </c>
@@ -1016,21 +1031,21 @@
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="24"/>
+      <c r="B14" s="28"/>
       <c r="C14" s="8"/>
       <c r="D14" s="9"/>
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
-      <c r="B15" s="24"/>
+      <c r="B15" s="28"/>
       <c r="C15" s="8"/>
       <c r="D15" s="9"/>
       <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
-      <c r="B16" s="25"/>
+      <c r="B16" s="29"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
       <c r="E16" s="10"/>
@@ -1039,16 +1054,16 @@
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="32"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="33">
         <v>45978</v>
       </c>
       <c r="C18" s="5">
@@ -1063,7 +1078,7 @@
       <c r="A19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="24"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="8">
         <v>40</v>
       </c>
@@ -1074,21 +1089,21 @@
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="24"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="8"/>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="24"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="8"/>
       <c r="D21" s="9"/>
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
-      <c r="B22" s="25"/>
+      <c r="B22" s="29"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
       <c r="E22" s="10"/>
@@ -1097,16 +1112,16 @@
       <c r="A23" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="33">
         <v>45985</v>
       </c>
       <c r="C24" s="5">
@@ -1123,7 +1138,7 @@
       <c r="A25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="24"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="8">
         <v>55</v>
       </c>
@@ -1138,7 +1153,7 @@
       <c r="A26" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="24"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="8">
         <v>20</v>
       </c>
@@ -1149,14 +1164,14 @@
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
-      <c r="B27" s="24"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
-      <c r="B28" s="25"/>
+      <c r="B28" s="29"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
       <c r="E28" s="10"/>
@@ -1165,42 +1180,66 @@
       <c r="A29" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="28"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="32"/>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
+      <c r="A30" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="27"/>
+      <c r="C30" s="13">
+        <v>15</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="9"/>
+      <c r="A31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="28"/>
+      <c r="C31" s="8">
+        <v>60</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="9"/>
+      <c r="A32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="8">
+        <v>55</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="E32" s="8"/>
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="9"/>
+      <c r="A33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="8">
+        <v>5</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="E33" s="8"/>
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
-      <c r="B34" s="25"/>
+      <c r="B34" s="29"/>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
@@ -1209,42 +1248,42 @@
       <c r="A35" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="28"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="32"/>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="23"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="5"/>
       <c r="D36" s="6"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
-      <c r="B37" s="24"/>
+      <c r="B37" s="28"/>
       <c r="C37" s="8"/>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
-      <c r="B38" s="24"/>
+      <c r="B38" s="28"/>
       <c r="C38" s="8"/>
       <c r="D38" s="9"/>
       <c r="E38" s="8"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
-      <c r="B39" s="24"/>
+      <c r="B39" s="28"/>
       <c r="C39" s="8"/>
       <c r="D39" s="9"/>
       <c r="E39" s="8"/>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
-      <c r="B40" s="25"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
       <c r="E40" s="10"/>
@@ -1253,42 +1292,42 @@
       <c r="A41" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="28"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="32"/>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="31"/>
+      <c r="B42" s="27"/>
       <c r="C42" s="5"/>
       <c r="D42" s="6"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
-      <c r="B43" s="24"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="8"/>
       <c r="D43" s="9"/>
       <c r="E43" s="8"/>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
-      <c r="B44" s="24"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="8"/>
       <c r="D44" s="9"/>
       <c r="E44" s="8"/>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
-      <c r="B45" s="24"/>
+      <c r="B45" s="28"/>
       <c r="C45" s="8"/>
       <c r="D45" s="9"/>
       <c r="E45" s="8"/>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="25"/>
+      <c r="B46" s="29"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11"/>
       <c r="E46" s="10"/>
@@ -1297,42 +1336,42 @@
       <c r="A47" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="28"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="32"/>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
-      <c r="B48" s="31"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="5"/>
       <c r="D48" s="6"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
-      <c r="B49" s="24"/>
+      <c r="B49" s="28"/>
       <c r="C49" s="8"/>
       <c r="D49" s="9"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
-      <c r="B50" s="24"/>
+      <c r="B50" s="28"/>
       <c r="C50" s="8"/>
       <c r="D50" s="9"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
-      <c r="B51" s="24"/>
+      <c r="B51" s="28"/>
       <c r="C51" s="8"/>
       <c r="D51" s="9"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
-      <c r="B52" s="25"/>
+      <c r="B52" s="29"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
       <c r="E52" s="10"/>
@@ -1341,42 +1380,42 @@
       <c r="A53" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="28"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="32"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
-      <c r="B54" s="31"/>
+      <c r="B54" s="27"/>
       <c r="C54" s="5"/>
       <c r="D54" s="6"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7"/>
-      <c r="B55" s="24"/>
+      <c r="B55" s="28"/>
       <c r="C55" s="8"/>
       <c r="D55" s="9"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7"/>
-      <c r="B56" s="24"/>
+      <c r="B56" s="28"/>
       <c r="C56" s="8"/>
       <c r="D56" s="9"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7"/>
-      <c r="B57" s="24"/>
+      <c r="B57" s="28"/>
       <c r="C57" s="8"/>
       <c r="D57" s="9"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
-      <c r="B58" s="25"/>
+      <c r="B58" s="29"/>
       <c r="C58" s="10"/>
       <c r="D58" s="11"/>
       <c r="E58" s="10"/>
@@ -1385,42 +1424,42 @@
       <c r="A59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="26"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="28"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="32"/>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13"/>
-      <c r="B60" s="31"/>
+      <c r="B60" s="27"/>
       <c r="C60" s="13"/>
       <c r="D60" s="14"/>
       <c r="E60" s="13"/>
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8"/>
-      <c r="B61" s="24"/>
+      <c r="B61" s="28"/>
       <c r="C61" s="8"/>
       <c r="D61" s="9"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8"/>
-      <c r="B62" s="24"/>
+      <c r="B62" s="28"/>
       <c r="C62" s="8"/>
       <c r="D62" s="9"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>
-      <c r="B63" s="24"/>
+      <c r="B63" s="28"/>
       <c r="C63" s="8"/>
       <c r="D63" s="9"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
-      <c r="B64" s="25"/>
+      <c r="B64" s="29"/>
       <c r="C64" s="8"/>
       <c r="D64" s="9"/>
       <c r="E64" s="8"/>
@@ -1429,19 +1468,19 @@
       <c r="A65" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B65" s="26"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="28"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="32"/>
     </row>
     <row r="66" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B66" s="30"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="15">
         <f>MROUND(SUM(C6:C65) /60,0.2)</f>
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="17"/>
@@ -1456,6 +1495,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:B52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="B59:E59"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -1472,15 +1520,6 @@
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:B40"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:B52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="B59:E59"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Durée par tranche de 10min" error="Le nombre doit être de type entier" sqref="C54:C58 C48:C52 C36:C40 C42:C46 C18:C22 B6 C12:C16 C6:C10 C30:C34 C60:C64 C24:C28" xr:uid="{345ABA8F-B69F-4AFC-9D0E-D2AB0ACDE277}">
@@ -1502,15 +1541,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A5B8F5EAAC22C48A11F5D9A60E6F21D" ma:contentTypeVersion="16" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="f2b963976306cc54294b7f4545a3c6c4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1b10758-7132-46a4-a2fe-7a2cf46f51f4" xmlns:ns3="f7d9f5a6-831d-4621-8c77-cbcaf993e406" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5e135fa2fc1295e1586ddcd9c1a8904" ns2:_="" ns3:_="">
     <xsd:import namespace="a1b10758-7132-46a4-a2fe-7a2cf46f51f4"/>
@@ -1753,6 +1783,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1765,14 +1804,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BCAAC0-9C03-42D2-8685-2E30F60CCBAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40597E6F-FA73-4A07-893F-099FDC15B64D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1791,6 +1822,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BCAAC0-9C03-42D2-8685-2E30F60CCBAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E6F7E92-72FE-4C94-B42F-AE9EA593DE95}">
   <ds:schemaRefs>

--- a/doc/T-Jercleuett-BitRuisseau-321.xlsx
+++ b/doc/T-Jercleuett-BitRuisseau-321.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pt04ihk\Documents\GitHub\321-BitRuisseau\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE6F43E-AF0D-4DF1-BA24-77A216CD1CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71F1C2E-B883-4320-92EB-73C6BBCAB484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="18" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
   <si>
     <t>Apprenti.e</t>
   </si>
@@ -182,6 +182,21 @@
   </si>
   <si>
     <t>JDT</t>
+  </si>
+  <si>
+    <t>Explications</t>
+  </si>
+  <si>
+    <t>Explications du prof au tableau</t>
+  </si>
+  <si>
+    <t>MediaPlayer</t>
+  </si>
+  <si>
+    <t>Implémentation du MediaPlayer et test avec des fichiers mp3</t>
+  </si>
+  <si>
+    <t>Commencer à implémenter MQTT pour réagir et envoyer des messages</t>
   </si>
 </sst>
 </file>
@@ -485,51 +500,51 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -862,10 +877,10 @@
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="23"/>
+      <c r="C1" s="32"/>
       <c r="D1" s="22" t="s">
         <v>1</v>
       </c>
@@ -877,10 +892,10 @@
       <c r="A2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="32"/>
       <c r="D2" s="22" t="s">
         <v>4</v>
       </c>
@@ -892,10 +907,10 @@
       <c r="A3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="23"/>
+      <c r="C3" s="32"/>
       <c r="D3" s="22" t="s">
         <v>7</v>
       </c>
@@ -907,12 +922,12 @@
       <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="26"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
     </row>
     <row r="5" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -935,7 +950,7 @@
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="23">
         <v>45964</v>
       </c>
       <c r="C6" s="5">
@@ -950,7 +965,7 @@
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="28"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="8">
         <v>50</v>
       </c>
@@ -963,7 +978,7 @@
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="28"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="8">
         <v>60</v>
       </c>
@@ -976,14 +991,14 @@
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
-      <c r="B9" s="28"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
       <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
-      <c r="B10" s="29"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="10"/>
       <c r="D10" s="11"/>
       <c r="E10" s="10"/>
@@ -992,16 +1007,16 @@
       <c r="A11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="28"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="23">
         <v>45971</v>
       </c>
       <c r="C12" s="5">
@@ -1018,7 +1033,7 @@
       <c r="A13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="28"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="8">
         <v>20</v>
       </c>
@@ -1031,21 +1046,21 @@
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
-      <c r="B14" s="28"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="8"/>
       <c r="D14" s="9"/>
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
-      <c r="B15" s="28"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="8"/>
       <c r="D15" s="9"/>
       <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
-      <c r="B16" s="29"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
       <c r="E16" s="10"/>
@@ -1054,16 +1069,16 @@
       <c r="A17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="32"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="23">
         <v>45978</v>
       </c>
       <c r="C18" s="5">
@@ -1078,7 +1093,7 @@
       <c r="A19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="28"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="8">
         <v>40</v>
       </c>
@@ -1089,21 +1104,21 @@
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="28"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="8"/>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="28"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="8"/>
       <c r="D21" s="9"/>
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
-      <c r="B22" s="29"/>
+      <c r="B22" s="25"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
       <c r="E22" s="10"/>
@@ -1112,16 +1127,16 @@
       <c r="A23" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="28"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="23">
         <v>45985</v>
       </c>
       <c r="C24" s="5">
@@ -1138,7 +1153,7 @@
       <c r="A25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="28"/>
+      <c r="B25" s="24"/>
       <c r="C25" s="8">
         <v>55</v>
       </c>
@@ -1153,7 +1168,7 @@
       <c r="A26" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="28"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="8">
         <v>20</v>
       </c>
@@ -1164,14 +1179,14 @@
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
-      <c r="B27" s="28"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
-      <c r="B28" s="29"/>
+      <c r="B28" s="25"/>
       <c r="C28" s="10"/>
       <c r="D28" s="11"/>
       <c r="E28" s="10"/>
@@ -1180,16 +1195,18 @@
       <c r="A29" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="32"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="28"/>
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="23">
+        <v>45992</v>
+      </c>
       <c r="C30" s="13">
         <v>15</v>
       </c>
@@ -1202,7 +1219,7 @@
       <c r="A31" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="24"/>
       <c r="C31" s="8">
         <v>60</v>
       </c>
@@ -1215,7 +1232,7 @@
       <c r="A32" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="28"/>
+      <c r="B32" s="24"/>
       <c r="C32" s="8">
         <v>55</v>
       </c>
@@ -1228,7 +1245,7 @@
       <c r="A33" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="24"/>
       <c r="C33" s="8">
         <v>5</v>
       </c>
@@ -1239,7 +1256,7 @@
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
-      <c r="B34" s="29"/>
+      <c r="B34" s="25"/>
       <c r="C34" s="8"/>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
@@ -1248,42 +1265,60 @@
       <c r="A35" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="32"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="28"/>
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="6"/>
+      <c r="A36" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="23">
+        <v>45999</v>
+      </c>
+      <c r="C36" s="5">
+        <v>20</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
+      <c r="A37" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="24"/>
+      <c r="C37" s="8">
+        <v>60</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="8">
+        <v>55</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="E38" s="8"/>
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
-      <c r="B39" s="28"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="8"/>
       <c r="D39" s="9"/>
       <c r="E39" s="8"/>
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
-      <c r="B40" s="29"/>
+      <c r="B40" s="25"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
       <c r="E40" s="10"/>
@@ -1292,42 +1327,42 @@
       <c r="A41" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="32"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="28"/>
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="27"/>
+      <c r="B42" s="31"/>
       <c r="C42" s="5"/>
       <c r="D42" s="6"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
-      <c r="B43" s="28"/>
+      <c r="B43" s="24"/>
       <c r="C43" s="8"/>
       <c r="D43" s="9"/>
       <c r="E43" s="8"/>
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
-      <c r="B44" s="28"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="8"/>
       <c r="D44" s="9"/>
       <c r="E44" s="8"/>
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
-      <c r="B45" s="28"/>
+      <c r="B45" s="24"/>
       <c r="C45" s="8"/>
       <c r="D45" s="9"/>
       <c r="E45" s="8"/>
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
-      <c r="B46" s="29"/>
+      <c r="B46" s="25"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11"/>
       <c r="E46" s="10"/>
@@ -1336,42 +1371,42 @@
       <c r="A47" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="30"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="32"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="28"/>
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
-      <c r="B48" s="27"/>
+      <c r="B48" s="31"/>
       <c r="C48" s="5"/>
       <c r="D48" s="6"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
-      <c r="B49" s="28"/>
+      <c r="B49" s="24"/>
       <c r="C49" s="8"/>
       <c r="D49" s="9"/>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
-      <c r="B50" s="28"/>
+      <c r="B50" s="24"/>
       <c r="C50" s="8"/>
       <c r="D50" s="9"/>
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
-      <c r="B51" s="28"/>
+      <c r="B51" s="24"/>
       <c r="C51" s="8"/>
       <c r="D51" s="9"/>
       <c r="E51" s="8"/>
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
-      <c r="B52" s="29"/>
+      <c r="B52" s="25"/>
       <c r="C52" s="10"/>
       <c r="D52" s="11"/>
       <c r="E52" s="10"/>
@@ -1380,42 +1415,42 @@
       <c r="A53" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="32"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="28"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
-      <c r="B54" s="27"/>
+      <c r="B54" s="31"/>
       <c r="C54" s="5"/>
       <c r="D54" s="6"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7"/>
-      <c r="B55" s="28"/>
+      <c r="B55" s="24"/>
       <c r="C55" s="8"/>
       <c r="D55" s="9"/>
       <c r="E55" s="8"/>
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7"/>
-      <c r="B56" s="28"/>
+      <c r="B56" s="24"/>
       <c r="C56" s="8"/>
       <c r="D56" s="9"/>
       <c r="E56" s="8"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7"/>
-      <c r="B57" s="28"/>
+      <c r="B57" s="24"/>
       <c r="C57" s="8"/>
       <c r="D57" s="9"/>
       <c r="E57" s="8"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
-      <c r="B58" s="29"/>
+      <c r="B58" s="25"/>
       <c r="C58" s="10"/>
       <c r="D58" s="11"/>
       <c r="E58" s="10"/>
@@ -1424,42 +1459,42 @@
       <c r="A59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="30"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="32"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="28"/>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13"/>
-      <c r="B60" s="27"/>
+      <c r="B60" s="31"/>
       <c r="C60" s="13"/>
       <c r="D60" s="14"/>
       <c r="E60" s="13"/>
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8"/>
-      <c r="B61" s="28"/>
+      <c r="B61" s="24"/>
       <c r="C61" s="8"/>
       <c r="D61" s="9"/>
       <c r="E61" s="8"/>
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8"/>
-      <c r="B62" s="28"/>
+      <c r="B62" s="24"/>
       <c r="C62" s="8"/>
       <c r="D62" s="9"/>
       <c r="E62" s="8"/>
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>
-      <c r="B63" s="28"/>
+      <c r="B63" s="24"/>
       <c r="C63" s="8"/>
       <c r="D63" s="9"/>
       <c r="E63" s="8"/>
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
-      <c r="B64" s="29"/>
+      <c r="B64" s="25"/>
       <c r="C64" s="8"/>
       <c r="D64" s="9"/>
       <c r="E64" s="8"/>
@@ -1468,19 +1503,19 @@
       <c r="A65" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B65" s="30"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="32"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="28"/>
     </row>
     <row r="66" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="34" t="s">
+      <c r="A66" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B66" s="35"/>
+      <c r="B66" s="30"/>
       <c r="C66" s="15">
         <f>MROUND(SUM(C6:C65) /60,0.2)</f>
-        <v>10.4</v>
+        <v>12.600000000000001</v>
       </c>
       <c r="D66" s="16"/>
       <c r="E66" s="17"/>
@@ -1495,15 +1530,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B36:B40"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:B52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="B59:E59"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -1520,6 +1546,15 @@
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:B40"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:B52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="B59:E59"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Durée par tranche de 10min" error="Le nombre doit être de type entier" sqref="C54:C58 C48:C52 C36:C40 C42:C46 C18:C22 B6 C12:C16 C6:C10 C30:C34 C60:C64 C24:C28" xr:uid="{345ABA8F-B69F-4AFC-9D0E-D2AB0ACDE277}">
@@ -1541,6 +1576,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A5B8F5EAAC22C48A11F5D9A60E6F21D" ma:contentTypeVersion="16" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="f2b963976306cc54294b7f4545a3c6c4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1b10758-7132-46a4-a2fe-7a2cf46f51f4" xmlns:ns3="f7d9f5a6-831d-4621-8c77-cbcaf993e406" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5e135fa2fc1295e1586ddcd9c1a8904" ns2:_="" ns3:_="">
     <xsd:import namespace="a1b10758-7132-46a4-a2fe-7a2cf46f51f4"/>
@@ -1783,15 +1827,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1804,6 +1839,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BCAAC0-9C03-42D2-8685-2E30F60CCBAA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40597E6F-FA73-4A07-893F-099FDC15B64D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1822,14 +1865,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38BCAAC0-9C03-42D2-8685-2E30F60CCBAA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E6F7E92-72FE-4C94-B42F-AE9EA593DE95}">
   <ds:schemaRefs>
